--- a/evals/fixtures/uart16550/spec/uart_regs.xlsx
+++ b/evals/fixtures/uart16550/spec/uart_regs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FCR</t>
+          <t>IIR</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -922,33 +922,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>fifo_en</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7:4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FIFO enable</t>
+          <t>Fixed top nibble (OpenCores synth)</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>rx_clr</t>
+          <t>fifo_en</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Clear RX FIFO</t>
+          <t>FIFO enable</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tx_clr</t>
+          <t>rx_clr</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Clear TX FIFO</t>
+          <t>Clear RX FIFO</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>trig</t>
+          <t>tx_clr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7:6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1080,25 +1080,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RX trigger level</t>
+          <t>Clear TX FIFO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>FCR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1106,17 +1106,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>wls</t>
+          <t>trig</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1:0</t>
+          <t>7:6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>WO</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Word length select</t>
+          <t>RX trigger level</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stb</t>
+          <t>wls</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1:0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Stop bits</t>
+          <t>Word length select</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pen</t>
+          <t>stb</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Parity enable</t>
+          <t>Stop bits</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>eps</t>
+          <t>pen</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Even parity select</t>
+          <t>Parity enable</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Break control</t>
+          <t>Even parity select</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>dlab</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1344,18 +1344,18 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Divisor latch access bit</t>
+          <t>Break control</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MCR</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
         <v>8</v>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>dtr</t>
+          <t>dlab</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Data terminal ready</t>
+          <t>Divisor latch access bit</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>rts</t>
+          <t>dtr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Request to send</t>
+          <t>Data terminal ready</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>loop</t>
+          <t>rts</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1476,43 +1476,43 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Loopback</t>
+          <t>Request to send</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LSR</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
         <v>8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>dr</t>
+          <t>loop</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Data ready</t>
+          <t>Loopback</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>oe</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Overrun error</t>
+          <t>Data ready</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>pe</t>
+          <t>oe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Parity error</t>
+          <t>Overrun error</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fe</t>
+          <t>pe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Framing error</t>
+          <t>Parity error</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>bi</t>
+          <t>fe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Break interrupt</t>
+          <t>Framing error</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>thre</t>
+          <t>bi</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1736,11 +1736,11 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Transmitter holding empty</t>
+          <t>Break interrupt</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>temt</t>
+          <t>thre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1784,18 +1784,18 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Transmitter empty</t>
+          <t>Transmitter holding empty</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>LSR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
         <v>8</v>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>cts</t>
+          <t>temt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1824,11 +1824,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Clear to send</t>
+          <t>Transmitter empty</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>dsr</t>
+          <t>cts</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1872,49 +1872,93 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Data set ready</t>
+          <t>Clear to send</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>24</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>dsr</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Data set ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>SCR</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" t="n">
         <v>28</v>
       </c>
-      <c r="C34" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>7:0</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Scratch register</t>
         </is>
